--- a/utils/monday_sprint_sprint_2026-07.xlsx
+++ b/utils/monday_sprint_sprint_2026-07.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="317">
   <si>
     <t>Ticket</t>
   </si>
@@ -108,60 +108,72 @@
     <t>Report técnico - Reunião</t>
   </si>
   <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>23/01/2026</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>36567</t>
+  </si>
+  <si>
+    <t>Abertura de linha no fluxo por operação de usinagem</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Link para chamar o procedimento para incluir o novo produto.</t>
+  </si>
+  <si>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>28/07/2025</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>29848</t>
+  </si>
+  <si>
+    <t>Alteração da referencia de Etiqueta para Romaneio</t>
+  </si>
+  <si>
+    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
     <t>Semana 5</t>
   </si>
   <si>
-    <t>36567</t>
-  </si>
-  <si>
-    <t>Abertura de linha no fluxo por operação de usinagem</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Link para chamar o procedimento para incluir o novo produto.</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>28/07/2025</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>29848</t>
-  </si>
-  <si>
-    <t>Alteração da referencia de Etiqueta para Romaneio</t>
-  </si>
-  <si>
-    <t>Boa tarde Precisamos que seja realizada a alteração do sistema abaixo onde faz a busca das etiquetas amarelas para os romaneios "ATIVO", desconsiderando o BOX 0. Deve aparecer disponível para vincular no ticket todos os romaneios do modelo/conjunto conforme as regras atuais do sistema. Também deve s</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
     <t>36213</t>
   </si>
   <si>
@@ -174,10 +186,7 @@
     <t>Enzo Luiz Okabe Auad</t>
   </si>
   <si>
-    <t>23/01/2026</t>
-  </si>
-  <si>
-    <t>15/04/2026</t>
+    <t>10/04/2026</t>
   </si>
   <si>
     <t>Link para chamar o procedimento para incluir o novo cliente</t>
@@ -198,9 +207,6 @@
     <t>27/11/2025</t>
   </si>
   <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
     <t>Novembro</t>
   </si>
   <si>
@@ -240,7 +246,7 @@
     <t>01/12/2025</t>
   </si>
   <si>
-    <t>25/03/2026</t>
+    <t>20/03/2026</t>
   </si>
   <si>
     <t>Semana 1</t>
@@ -282,7 +288,7 @@
     <t>19/09/2025</t>
   </si>
   <si>
-    <t>27/04/2026</t>
+    <t>22/04/2026</t>
   </si>
   <si>
     <t>Setembro</t>
@@ -297,9 +303,6 @@
     <t>Boa tarde, Solicito um chamado para fazer automatização dos dados Hora ponto X Horas apontadas, com uma média mínima de 75% de apontamento. E ao mesmo tempo uma análise de total de ordens baixadas, ordens pendentes e somatório das ordens (baixadas/pendentes). Em anexos, está um modelo que estamos us</t>
   </si>
   <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
     <t>31270</t>
   </si>
   <si>
@@ -333,81 +336,75 @@
     <t>IDENTIFICADOR ESPECIAL - LOT NUMBER - Reunião</t>
   </si>
   <si>
-    <t>Bom dia, Favor criar um sistema de cadastro de identificador especial similar ao já existente da tela de cadastro TCPP45ID e consulta WCPP221J: Favor criar uma nova opção na tela TCPP45ID denominada "Possui controle ID especial?", sendo que se respondida como "SIM" permita o preenchimento dos seguin</t>
+    <t>35764</t>
+  </si>
+  <si>
+    <t>Automação da lista de presença - Detalhar escopo</t>
+  </si>
+  <si>
+    <t>31699</t>
+  </si>
+  <si>
+    <t>Cadastro de TOKEN Ailton</t>
+  </si>
+  <si>
+    <t>34651</t>
+  </si>
+  <si>
+    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
+  </si>
+  <si>
+    <t>Incluir no cadastro do item da proposta a chamada do link (item 5.3)</t>
+  </si>
+  <si>
+    <t>Link para chamar o procedimento para incluir nova oportunidade</t>
+  </si>
+  <si>
+    <t>Incluir no cadastro de clientes a chamada do link (item 1.4)</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>36125</t>
+  </si>
+  <si>
+    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
+  </si>
+  <si>
+    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>19/01/2026</t>
+  </si>
+  <si>
+    <t>36320</t>
+  </si>
+  <si>
+    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem) - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>36201</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
   </si>
   <si>
     <t>Willian Gabriel Paixão dos Santos</t>
   </si>
   <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
-    <t>35764</t>
-  </si>
-  <si>
-    <t>Automação da lista de presença - Detalhar escopo</t>
-  </si>
-  <si>
-    <t>31699</t>
-  </si>
-  <si>
-    <t>Cadastro de TOKEN Ailton</t>
-  </si>
-  <si>
-    <t>34651</t>
-  </si>
-  <si>
-    <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
-  </si>
-  <si>
-    <t>Incluir no cadastro do item da proposta a chamada do link (item 5.3)</t>
-  </si>
-  <si>
-    <t>Link para chamar o procedimento para incluir nova oportunidade</t>
-  </si>
-  <si>
-    <t>Incluir no cadastro de clientes a chamada do link (item 1.4)</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>36125</t>
-  </si>
-  <si>
-    <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
-  </si>
-  <si>
-    <t>Boa tarde Flavio, Dando um retorno da nossa conversa por telefone, teremos o apontamento de % para todas as operações que engloba a operação escarfagem (escarfagem, queimar areia etc.) Se deixarmos alguma operação de escarfagem fora, abre uma brecha para escarfar sem a visualização da % executada. C</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>19/01/2026</t>
-  </si>
-  <si>
-    <t>36320</t>
-  </si>
-  <si>
-    <t>Linkar gatilho de ACR com TV manutenções (Central + Usinagem) - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Estou solicitando que façamos um link entre os gatilhos de ACR e a gestão visual nas TVs. A ideia é implementar gestão visual além da tarja amarela, sinalizando visualmente quando algum dos gatilhos forem atingidos (Tempo e frequencia) Att,</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>36201</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
-  </si>
-  <si>
     <t>36197</t>
   </si>
   <si>
@@ -471,9 +468,6 @@
     <t>TEMPOS PADRÕES DE ACABAMENTO</t>
   </si>
   <si>
-    <t>Bom dia, Favor correlacionar os tempos totais que estão no roteiro na coluna "Tempo Planejado" com os dados da planilha anexa, realizar a divisão no sistema que controla os tempos das atividades complementares. A planilha anexa separa os tempos por liga, favor verificarem se é possível criar essa re</t>
-  </si>
-  <si>
     <t>36313</t>
   </si>
   <si>
@@ -495,7 +489,7 @@
     <t>28/01/2026</t>
   </si>
   <si>
-    <t>04/03/2026</t>
+    <t>27/02/2026</t>
   </si>
   <si>
     <t>35792</t>
@@ -513,7 +507,7 @@
     <t>18/12/2025</t>
   </si>
   <si>
-    <t>29/03/2026</t>
+    <t>24/03/2026</t>
   </si>
   <si>
     <t>35808</t>
@@ -567,7 +561,7 @@
     <t>20/01/2026</t>
   </si>
   <si>
-    <t>10/03/2026</t>
+    <t>05/03/2026</t>
   </si>
   <si>
     <t>35097</t>
@@ -708,7 +702,7 @@
     <t>27/01/2026</t>
   </si>
   <si>
-    <t>22/03/2026</t>
+    <t>17/03/2026</t>
   </si>
   <si>
     <t>36245</t>
@@ -765,12 +759,6 @@
     <t>Tempo de parada Carrossel</t>
   </si>
   <si>
-    <t>Verificar ao retomar o apontamento o tempo de parada está como 1seg, mesmo tendo parado por mais de 10min</t>
-  </si>
-  <si>
-    <t>06/02/2026</t>
-  </si>
-  <si>
     <t>ALTC - Adicionar Botão PDI</t>
   </si>
   <si>
@@ -855,7 +843,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Homologação</t>
@@ -879,7 +867,7 @@
     <t>06/11/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>36366</t>
@@ -894,7 +882,7 @@
     <t>30/01/2026</t>
   </si>
   <si>
-    <t>11/03/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>Dashboard de Change Log - Governança de TI</t>
@@ -1507,42 +1495,42 @@
         <v>29</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -1554,13 +1542,13 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>24</v>
@@ -1578,7 +1566,7 @@
         <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>24</v>
@@ -1586,7 +1574,7 @@
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -1598,7 +1586,7 @@
         <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>24</v>
@@ -1607,30 +1595,30 @@
         <v>20</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -1642,31 +1630,31 @@
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -1674,7 +1662,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
@@ -1686,25 +1674,25 @@
         <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1718,7 +1706,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1730,7 +1718,7 @@
         <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>24</v>
@@ -1739,30 +1727,30 @@
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
@@ -1774,39 +1762,39 @@
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="L9" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1818,39 +1806,39 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -1862,39 +1850,39 @@
         <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -1906,10 +1894,10 @@
         <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1930,7 +1918,7 @@
         <v>25</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>24</v>
@@ -1938,7 +1926,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1950,39 +1938,39 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -1994,31 +1982,31 @@
         <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M14" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>24</v>
@@ -2026,7 +2014,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -2038,39 +2026,39 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -2082,28 +2070,28 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>94</v>
+        <v>32</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>26</v>
@@ -2114,7 +2102,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -2126,13 +2114,13 @@
         <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>24</v>
@@ -2150,7 +2138,7 @@
         <v>25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>24</v>
@@ -2158,7 +2146,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -2170,10 +2158,10 @@
         <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2191,10 +2179,10 @@
         <v>24</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>24</v>
@@ -2202,7 +2190,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2214,39 +2202,39 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2255,10 +2243,10 @@
         <v>29</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>106</v>
@@ -2267,30 +2255,30 @@
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2302,10 +2290,10 @@
         <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2323,10 +2311,10 @@
         <v>24</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>24</v>
@@ -2334,7 +2322,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2346,13 +2334,13 @@
         <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>24</v>
@@ -2367,10 +2355,10 @@
         <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>24</v>
@@ -2378,7 +2366,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2390,10 +2378,10 @@
         <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2411,10 +2399,10 @@
         <v>24</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>24</v>
@@ -2422,7 +2410,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2434,7 +2422,7 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>24</v>
@@ -2443,30 +2431,30 @@
         <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2478,7 +2466,7 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>24</v>
@@ -2487,30 +2475,30 @@
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2522,7 +2510,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>24</v>
@@ -2531,25 +2519,25 @@
         <v>20</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2566,7 +2554,7 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>19</v>
@@ -2598,7 +2586,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2610,31 +2598,31 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>27</v>
@@ -2642,7 +2630,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2654,31 +2642,31 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -2686,7 +2674,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2698,16 +2686,16 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>22</v>
@@ -2716,10 +2704,10 @@
         <v>23</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L30" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>26</v>
@@ -2730,7 +2718,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2742,16 +2730,16 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>22</v>
@@ -2760,7 +2748,7 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2774,51 +2762,51 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="G32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="G32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="2" t="s">
+      <c r="I32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J32" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="I32" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="K32" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2830,7 +2818,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>24</v>
@@ -2839,30 +2827,30 @@
         <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2874,31 +2862,31 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F34" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="G34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="2" t="s">
+      <c r="I34" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J34" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="I34" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L34" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="K34" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="L34" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="M34" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>27</v>
@@ -2906,7 +2894,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2918,13 +2906,13 @@
         <v>24</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>24</v>
@@ -2939,10 +2927,10 @@
         <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>24</v>
@@ -2950,51 +2938,51 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M36" s="2" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>70</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3006,10 +2994,10 @@
         <v>24</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -3027,10 +3015,10 @@
         <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>24</v>
@@ -3038,7 +3026,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -3050,28 +3038,28 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="2" t="s">
         <v>156</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -3082,7 +3070,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -3094,39 +3082,39 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>162</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -3138,39 +3126,39 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -3182,10 +3170,10 @@
         <v>24</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3206,7 +3194,7 @@
         <v>25</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>24</v>
@@ -3214,51 +3202,51 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3270,7 +3258,7 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>24</v>
@@ -3279,30 +3267,30 @@
         <v>20</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L43" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3314,31 +3302,31 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I44" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -3346,51 +3334,51 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>186</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>188</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3402,75 +3390,75 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H46" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>27</v>
@@ -3478,95 +3466,95 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J48" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="K48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N48" s="2" t="s">
         <v>200</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M49" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3578,22 +3566,22 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>24</v>
@@ -3602,15 +3590,15 @@
         <v>25</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3622,22 +3610,22 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>24</v>
@@ -3646,15 +3634,15 @@
         <v>25</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3666,10 +3654,10 @@
         <v>24</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3690,7 +3678,7 @@
         <v>25</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>24</v>
@@ -3698,7 +3686,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3710,39 +3698,39 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>190</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>192</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3754,7 +3742,7 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>24</v>
@@ -3763,30 +3751,30 @@
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K54" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M54" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3798,39 +3786,39 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3842,25 +3830,25 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H56" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>225</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3874,7 +3862,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3886,28 +3874,28 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>26</v>
@@ -3918,37 +3906,37 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B58" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="G58" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H58" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>236</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3962,7 +3950,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3974,25 +3962,25 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -4006,7 +3994,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -4018,31 +4006,31 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N60" s="2" t="s">
         <v>27</v>
@@ -4050,7 +4038,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -4062,10 +4050,10 @@
         <v>24</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>20</v>
@@ -4086,7 +4074,7 @@
         <v>25</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>24</v>
@@ -4094,7 +4082,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -4106,31 +4094,31 @@
         <v>24</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G62" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M62" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>24</v>
@@ -4138,7 +4126,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -4147,25 +4135,25 @@
         <v>29</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>251</v>
+        <v>24</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>24</v>
@@ -4174,15 +4162,15 @@
         <v>25</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4194,31 +4182,31 @@
         <v>24</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G64" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L64" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L64" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M64" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>24</v>
@@ -4226,7 +4214,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4238,31 +4226,31 @@
         <v>24</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G65" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L65" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L65" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M65" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>24</v>
@@ -4270,7 +4258,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4282,10 +4270,10 @@
         <v>24</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4306,7 +4294,7 @@
         <v>25</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>24</v>
@@ -4314,7 +4302,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4326,31 +4314,31 @@
         <v>24</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L67" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L67" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M67" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>24</v>
@@ -4358,7 +4346,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4370,7 +4358,7 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>24</v>
@@ -4379,30 +4367,30 @@
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4414,31 +4402,31 @@
         <v>24</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G69" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L69" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L69" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M69" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>24</v>
@@ -4446,7 +4434,7 @@
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4458,31 +4446,31 @@
         <v>24</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G70" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="H70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>31</v>
-      </c>
       <c r="M70" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>24</v>
@@ -4490,7 +4478,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4502,7 +4490,7 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>24</v>
@@ -4511,30 +4499,30 @@
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M71" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4546,54 +4534,54 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N72" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H72" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L72" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N72" s="2" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4611,10 +4599,10 @@
         <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>24</v>
@@ -4622,7 +4610,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4634,7 +4622,7 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>24</v>
@@ -4643,45 +4631,45 @@
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K74" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M74" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
@@ -4699,10 +4687,10 @@
         <v>24</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>24</v>
@@ -4710,7 +4698,7 @@
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4722,7 +4710,7 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>24</v>
@@ -4731,45 +4719,45 @@
         <v>20</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M76" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -4787,10 +4775,10 @@
         <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>24</v>
@@ -4798,7 +4786,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4810,83 +4798,83 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="K79" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="L79" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4898,31 +4886,31 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>27</v>
@@ -4941,23 +4929,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -4965,16 +4953,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -4993,12 +4981,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K22">
         <v>38</v>
@@ -5006,7 +4994,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -5014,7 +5002,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5045,12 +5033,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B2">
         <v>79</v>
@@ -5074,25 +5062,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5109,28 +5097,28 @@
         <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N10">
         <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -5141,13 +5129,13 @@
         <v>11</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H11">
         <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="K11">
         <v>79</v>
@@ -5159,15 +5147,15 @@
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="Q11">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -5179,33 +5167,33 @@
         <v>54</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N12">
         <v>4</v>
       </c>
       <c r="P12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="Q12">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N13">
         <v>7</v>
@@ -5214,32 +5202,32 @@
         <v>26</v>
       </c>
       <c r="Q13">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="7:17" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="Q14">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="N15">
         <v>1</v>
@@ -5247,7 +5235,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5255,7 +5243,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5263,7 +5251,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5274,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5282,49 +5270,49 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
@@ -5333,91 +5321,91 @@
         <v>458</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-07.xlsx
+++ b/utils/monday_sprint_sprint_2026-07.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1291" uniqueCount="296">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -63,114 +63,120 @@
     <t>36206</t>
   </si>
   <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>36232</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Report técnico - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>29/01/2026</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>11235541400</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Solicitação de serviço</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - API</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>Sistemas</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Abertura de linha no fluxo por operação de usinagem</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Link para chamar o procedimento para incluir o novo produto.</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>36232</t>
-  </si>
-  <si>
-    <t>Melhoria</t>
-  </si>
-  <si>
-    <t>Report técnico - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde, Solicito um chamado para automatizar a tabela de report técnico, em anexo, no e-mail. Esses dados são retirados do nosso sistema de manutenção e está apto a melhoria. Se possível, com as informações gerar um Dashboard. A ideia seria analisar mais dados com um número maior de ordens por ma</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>29/01/2026</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Não</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>36567</t>
-  </si>
-  <si>
-    <t>Categoria não informada</t>
-  </si>
-  <si>
-    <t>Abertura de linha no fluxo por operação de usinagem</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Solicitante não informado</t>
-  </si>
-  <si>
-    <t>Equipe não informada</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Link para chamar o procedimento para incluir o novo produto.</t>
-  </si>
-  <si>
     <t>Laura Herrmann Schmickler</t>
   </si>
   <si>
+    <t>11/02/2026</t>
+  </si>
+  <si>
     <t>29848</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>Alteração da referencia de Etiqueta para Romaneio</t>
   </si>
   <si>
@@ -189,6 +195,9 @@
     <t>36213</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>Alteração no sistema de manutenção</t>
   </si>
   <si>
@@ -207,6 +216,9 @@
     <t>35467</t>
   </si>
   <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
     <t>Alterar Cálculo do Custo de SUCATA RETORNO</t>
   </si>
   <si>
@@ -219,6 +231,9 @@
     <t>35738</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
     <t>Melhoria apontamento de corte de canais</t>
   </si>
   <si>
@@ -243,7 +258,7 @@
     <t>20/03/2026</t>
   </si>
   <si>
-    <t>35602</t>
+    <t>11235574514</t>
   </si>
   <si>
     <t>Sistema de reconhecimento e conferência</t>
@@ -258,7 +273,7 @@
     <t>Bom dia, Visando a qualidade de apontamento para os apontamentos do IROG do Tratamento térmico no BI, precisamos fazer melhorias no sistema atual. Deixar e usar os papéis. 1. Passar o checklist que hoje e físico para o virtual. Abaixo a foto do checklist. Lembrando que s~]ao 3 etapas que esse checkl</t>
   </si>
   <si>
-    <t>34073</t>
+    <t>11235578616</t>
   </si>
   <si>
     <t>Siga - Consulta Sequencia (Alt c)</t>
@@ -285,7 +300,7 @@
     <t>Boa tarde, Solicito um chamado para fazer automatização dos dados Hora ponto X Horas apontadas, com uma média mínima de 75% de apontamento. E ao mesmo tempo uma análise de total de ordens baixadas, ordens pendentes e somatório das ordens (baixadas/pendentes). Em anexos, está um modelo que estamos us</t>
   </si>
   <si>
-    <t>31270</t>
+    <t>10977158398</t>
   </si>
   <si>
     <t>MELHORIAS FLUXO 109 REVISÕES</t>
@@ -294,37 +309,46 @@
     <t>12/01/2026</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>11235596944</t>
   </si>
   <si>
     <t>Controle de pátio - Recebimento</t>
   </si>
   <si>
-    <t>35081</t>
+    <t>12/02/2026</t>
+  </si>
+  <si>
+    <t>11235589131</t>
   </si>
   <si>
     <t>SUGESTÃO PARA MELHORIA NA H5000</t>
   </si>
   <si>
-    <t>36055</t>
+    <t>11133867694</t>
   </si>
   <si>
     <t>IDENTIFICADOR ESPECIAL - LOT NUMBER - Reunião</t>
   </si>
   <si>
-    <t>35764</t>
+    <t>19/02/2026</t>
+  </si>
+  <si>
+    <t>11235596085</t>
   </si>
   <si>
     <t>Automação da lista de presença - Detalhar escopo</t>
   </si>
   <si>
-    <t>31699</t>
+    <t>16/02/2026</t>
+  </si>
+  <si>
+    <t>11235576700</t>
   </si>
   <si>
     <t>Cadastro de TOKEN Ailton</t>
   </si>
   <si>
-    <t>34651</t>
+    <t>11235564327</t>
   </si>
   <si>
     <t>Acesso a movimentação das moldagens apenas para uma lista de colaboradores</t>
@@ -333,6 +357,9 @@
     <t>Incluir no cadastro do item da proposta a chamada do link (item 5.3)</t>
   </si>
   <si>
+    <t>17/02/2026</t>
+  </si>
+  <si>
     <t>Link para chamar o procedimento para incluir nova oportunidade</t>
   </si>
   <si>
@@ -345,9 +372,6 @@
     <t>36125</t>
   </si>
   <si>
-    <t>Fundição</t>
-  </si>
-  <si>
     <t>OPÇÃO DE APONTAR % PARA OPERAÇÃO DE ESCRAFAGEM USE/KOMATSU</t>
   </si>
   <si>
@@ -429,25 +453,28 @@
     <t>Fazendo</t>
   </si>
   <si>
-    <t>36046</t>
+    <t>11235591834</t>
   </si>
   <si>
     <t>Aprimoramento Ailton - Valorização de modelos</t>
   </si>
   <si>
-    <t>35518</t>
+    <t>11235564701</t>
   </si>
   <si>
     <t>TEMPOS PADRÕES DE ACABAMENTO</t>
   </si>
   <si>
-    <t>36313</t>
+    <t>18/02/2026</t>
+  </si>
+  <si>
+    <t>11134105896</t>
   </si>
   <si>
     <t>Melhoria Sistema Custeio - Inspeção (Qualidade)</t>
   </si>
   <si>
-    <t>36310</t>
+    <t>11134144856</t>
   </si>
   <si>
     <t>Incluir o CC. 60.300 dentro de Compras e em Consequência dentro da Gerencia Supply - Reunião</t>
@@ -480,7 +507,7 @@
     <t>Fernanda da Costa Rodrigues</t>
   </si>
   <si>
-    <t>36309</t>
+    <t>11134166391</t>
   </si>
   <si>
     <t>Arquivo para subir AIlton</t>
@@ -501,18 +528,12 @@
     <t>Incluir no cadastro de proposta a chamada do link (item 4.3)</t>
   </si>
   <si>
-    <t>36157</t>
+    <t>11236575346</t>
   </si>
   <si>
     <t>Desenvolver alerta de tempo excedido com "alarme" na tela das linhas Fast Loop e Carrossel</t>
   </si>
   <si>
-    <t>Acrescentar opção de apontamento de % nas linhas UPR, disponibilizar lista de 10 em 10%. A soma não pode ultrapassar os 100%.</t>
-  </si>
-  <si>
-    <t>05/03/2026</t>
-  </si>
-  <si>
     <t>35097</t>
   </si>
   <si>
@@ -558,7 +579,10 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>31836</t>
+    <t>22/02/2026</t>
+  </si>
+  <si>
+    <t>11235597769</t>
   </si>
   <si>
     <t>Melhoria WMS - Conferencia e Carregamento</t>
@@ -585,7 +609,7 @@
     <t>Bom dia, Gentileza fazer o vínculo de atualização da aplicação - Logistica &gt; 2 - Reconhecimento de Receita Root/QVD/EXTRACAO/NFEDESP.qvd] - Nota fiscal Root/QVD/EXTRACAO/CPC389.qvd] - Invoice Root/QVD/EXTRACAO/CTEEMIT.qvd] - Cte (Obs: o chamado 36196 possui 02 campos novos que quando feitos precisam</t>
   </si>
   <si>
-    <t>33271</t>
+    <t>11235573349</t>
   </si>
   <si>
     <t>Alinhamento dos cálculos de disponibilidade</t>
@@ -663,24 +687,27 @@
     <t>Bom dia, Favor acrescentar um botão para visualizar as cargas que já foram finalizadas no forno, junto ao lado do apontamento de parada. Essa função também temos disponível no sistema antigo do tratamento térmico. Atenciosamente,</t>
   </si>
   <si>
-    <t>33331</t>
+    <t>11235576494</t>
   </si>
   <si>
     <t>[APS] - Criação de campo no ERP CÓDIGO DISPOSITIVO</t>
   </si>
   <si>
+    <t>11247251920</t>
+  </si>
+  <si>
     <t>ALTC - Adicionar consulta de corrida/forno/ano</t>
   </si>
   <si>
-    <t>11/02/2026</t>
-  </si>
-  <si>
-    <t>36526</t>
+    <t>11235361797</t>
   </si>
   <si>
     <t>Tempo de parada Carrossel</t>
   </si>
   <si>
+    <t>11247239027</t>
+  </si>
+  <si>
     <t>ALTC - Adicionar Botão PDI</t>
   </si>
   <si>
@@ -696,30 +723,36 @@
     <t>DESENVOLVIMENTO DE CONTROLE DE DISPOSITIVOS DE USINAGEM</t>
   </si>
   <si>
+    <t>11247252086</t>
+  </si>
+  <si>
     <t>ALTC - Adicionar Cargas de tratamento térmico F8</t>
   </si>
   <si>
     <t>Link para chamar o procedimento para incluir o novo item da proposta.</t>
   </si>
   <si>
-    <t>31977</t>
+    <t>11247046877</t>
   </si>
   <si>
     <t>Alterações no registro de moldagem via APP</t>
   </si>
   <si>
+    <t>11247261871</t>
+  </si>
+  <si>
     <t>ALTC - Verificar refugo no LOG</t>
   </si>
   <si>
     <t>Somente levar proposta se existir a Oportunidade</t>
   </si>
   <si>
-    <t>12/02/2026</t>
-  </si>
-  <si>
     <t>28392</t>
   </si>
   <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
     <t>Notas de consignado - Medição NIMBI</t>
   </si>
   <si>
@@ -729,6 +762,9 @@
     <t>Jessica Priscila Gonçalves</t>
   </si>
   <si>
+    <t>11247316021</t>
+  </si>
+  <si>
     <t>Novo Sistema</t>
   </si>
   <si>
@@ -738,16 +774,22 @@
     <t>Ajustar o envio de oportunidade para levar a fase que a oportunidade está (funil de vendas).</t>
   </si>
   <si>
+    <t>11247324972</t>
+  </si>
+  <si>
     <t>Não esta gerando numero de ordem de coleta no arquivo</t>
   </si>
   <si>
     <t>Ajustar as oportunidades já enviadas com a fase da oportunidade.</t>
   </si>
   <si>
+    <t>11247322677</t>
+  </si>
+  <si>
     <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>11258873607</t>
   </si>
   <si>
     <t>Criar KB Genexus especifica para Registro de pinturas</t>
@@ -756,40 +798,25 @@
     <t>Homologação</t>
   </si>
   <si>
-    <t>35128</t>
+    <t>11021399682</t>
   </si>
   <si>
     <t>Altona || Conferência Entrada de Consignados - Melhoria</t>
   </si>
   <si>
-    <t>Bom dia, Sandro! Dando continuidade ao processo de melhoria nas conferências do estoque peço que insiras no relatório abaixo: duas colunas conforme descrição abaixo e planilha anexa: 1) Finalidade (MP/C) - esse parâmetro servirá para conferir se um produto está classificado corretamente e consequent</t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
     <t>16/01/2026</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
     <t>Semana 3</t>
   </si>
   <si>
-    <t>36366</t>
+    <t>11303351346</t>
   </si>
   <si>
     <t>VISUALIZAÇÃO DE PORCENTAGEM E TEMPO DISPONIVEL APONTAMENTO ELETRONICO USE</t>
   </si>
   <si>
-    <t>Boa tarde, Para melhorar visualização dos operadores, precisamos de um campo que mostre o percentual disponível e o tempo ainda disponível da peça referente ao tempo padrão. Tela para mostrar os dados solicitados após indicar sequência, caso ultrapasse o tempo disponível (padrão) retornar 0 hrs. Qua</t>
-  </si>
-  <si>
-    <t>18/02/2026</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
+    <t>20/02/2026</t>
   </si>
   <si>
     <t>Dashboard de Change Log - Governança de TI</t>
@@ -798,7 +825,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2026-07</t>
+    <t>Jan/2026</t>
   </si>
   <si>
     <t>Base</t>
@@ -852,16 +879,13 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
     <t>Abertos</t>
   </si>
   <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
     <t>Baixa</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
   </si>
   <si>
     <t>Não definida</t>
@@ -1390,27 +1414,27 @@
         <v>24</v>
       </c>
       <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M2" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>31</v>
@@ -1443,21 +1467,21 @@
         <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>31</v>
@@ -1484,19 +1508,19 @@
         <v>24</v>
       </c>
       <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -1504,7 +1528,7 @@
         <v>47</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>31</v>
@@ -1513,10 +1537,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>21</v>
@@ -1531,27 +1555,27 @@
         <v>24</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>31</v>
@@ -1560,19 +1584,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -1581,24 +1605,24 @@
         <v>36</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>31</v>
@@ -1607,16 +1631,16 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
@@ -1625,19 +1649,19 @@
         <v>24</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1645,7 +1669,7 @@
         <v>47</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>31</v>
@@ -1654,10 +1678,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
@@ -1672,27 +1696,27 @@
         <v>24</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>31</v>
@@ -1701,45 +1725,45 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>31</v>
@@ -1748,16 +1772,16 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
@@ -1766,27 +1790,27 @@
         <v>24</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>31</v>
@@ -1795,16 +1819,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
@@ -1813,27 +1837,27 @@
         <v>24</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>31</v>
@@ -1842,10 +1866,10 @@
         <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>21</v>
@@ -1860,27 +1884,27 @@
         <v>24</v>
       </c>
       <c r="K12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L12" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>31</v>
@@ -1889,16 +1913,16 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
@@ -1907,27 +1931,27 @@
         <v>24</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>17</v>
@@ -1936,10 +1960,10 @@
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>44</v>
@@ -1954,27 +1978,27 @@
         <v>24</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>31</v>
@@ -1983,16 +2007,16 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
@@ -2001,27 +2025,27 @@
         <v>35</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="O15" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>31</v>
@@ -2030,10 +2054,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
@@ -2048,27 +2072,27 @@
         <v>35</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="O16" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O16" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>31</v>
@@ -2077,10 +2101,10 @@
         <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>44</v>
@@ -2092,30 +2116,30 @@
         <v>46</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L17" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M17" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>17</v>
@@ -2124,10 +2148,10 @@
         <v>42</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>21</v>
@@ -2142,27 +2166,27 @@
         <v>24</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>31</v>
@@ -2171,10 +2195,10 @@
         <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
@@ -2189,27 +2213,27 @@
         <v>24</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>31</v>
@@ -2218,10 +2242,10 @@
         <v>42</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
@@ -2236,27 +2260,27 @@
         <v>35</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="O20" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O20" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>31</v>
@@ -2265,10 +2289,10 @@
         <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>21</v>
@@ -2283,27 +2307,27 @@
         <v>24</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>17</v>
@@ -2312,10 +2336,10 @@
         <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>44</v>
@@ -2330,27 +2354,27 @@
         <v>24</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>31</v>
@@ -2359,10 +2383,10 @@
         <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>21</v>
@@ -2377,19 +2401,19 @@
         <v>24</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L23" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -2397,7 +2421,7 @@
         <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>31</v>
@@ -2406,10 +2430,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
@@ -2424,19 +2448,19 @@
         <v>24</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -2444,7 +2468,7 @@
         <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>31</v>
@@ -2453,10 +2477,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
@@ -2471,19 +2495,19 @@
         <v>24</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -2491,7 +2515,7 @@
         <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>31</v>
@@ -2500,10 +2524,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>21</v>
@@ -2518,19 +2542,19 @@
         <v>24</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -2547,7 +2571,7 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>20</v>
@@ -2565,27 +2589,27 @@
         <v>24</v>
       </c>
       <c r="K27" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L27" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M27" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>31</v>
@@ -2594,16 +2618,16 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
@@ -2612,27 +2636,27 @@
         <v>24</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>31</v>
@@ -2641,16 +2665,16 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
@@ -2659,27 +2683,27 @@
         <v>35</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N29" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="O29" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>31</v>
@@ -2688,16 +2712,16 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>23</v>
@@ -2712,21 +2736,21 @@
         <v>37</v>
       </c>
       <c r="M30" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N30" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="O30" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>31</v>
@@ -2735,16 +2759,16 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
@@ -2753,66 +2777,66 @@
         <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O31" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2820,7 +2844,7 @@
         <v>47</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>31</v>
@@ -2829,10 +2853,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
@@ -2847,27 +2871,27 @@
         <v>24</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>31</v>
@@ -2876,45 +2900,45 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>17</v>
@@ -2923,10 +2947,10 @@
         <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>44</v>
@@ -2941,27 +2965,27 @@
         <v>24</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>31</v>
@@ -2970,10 +2994,10 @@
         <v>42</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>44</v>
@@ -2988,27 +3012,27 @@
         <v>24</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>31</v>
@@ -3017,10 +3041,10 @@
         <v>42</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
@@ -3035,27 +3059,27 @@
         <v>35</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N37" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N37" s="2" t="s">
+      <c r="O37" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O37" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>31</v>
@@ -3064,10 +3088,10 @@
         <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
@@ -3082,27 +3106,27 @@
         <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M38" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N38" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N38" s="2" t="s">
+      <c r="O38" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O38" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>31</v>
@@ -3111,16 +3135,16 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
@@ -3129,27 +3153,27 @@
         <v>24</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O39" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>31</v>
@@ -3158,16 +3182,16 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
@@ -3176,27 +3200,27 @@
         <v>24</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L40" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O40" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>31</v>
@@ -3205,10 +3229,10 @@
         <v>42</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
@@ -3223,45 +3247,45 @@
         <v>35</v>
       </c>
       <c r="K41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L41" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M41" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O41" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O41" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>16</v>
+        <v>126</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>23</v>
@@ -3270,19 +3294,19 @@
         <v>24</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O42" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -3290,7 +3314,7 @@
         <v>47</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>31</v>
@@ -3299,10 +3323,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>21</v>
@@ -3317,92 +3341,92 @@
         <v>24</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>165</v>
+        <v>24</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O44" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>23</v>
@@ -3411,27 +3435,27 @@
         <v>24</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>31</v>
@@ -3440,16 +3464,16 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
@@ -3461,42 +3485,42 @@
         <v>36</v>
       </c>
       <c r="L46" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
@@ -3505,86 +3529,86 @@
         <v>24</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
@@ -3599,27 +3623,27 @@
         <v>24</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>25</v>
+        <v>188</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O49" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>31</v>
@@ -3628,45 +3652,45 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>24</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O50" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>31</v>
@@ -3675,16 +3699,16 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
@@ -3693,27 +3717,27 @@
         <v>24</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O51" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>31</v>
@@ -3722,10 +3746,10 @@
         <v>42</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>21</v>
@@ -3740,27 +3764,27 @@
         <v>24</v>
       </c>
       <c r="K52" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L52" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M52" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>31</v>
@@ -3769,16 +3793,16 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
@@ -3793,13 +3817,13 @@
         <v>37</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O53" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -3807,7 +3831,7 @@
         <v>47</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>31</v>
@@ -3816,10 +3840,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
@@ -3834,27 +3858,27 @@
         <v>24</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O54" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>31</v>
@@ -3863,16 +3887,16 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>23</v>
@@ -3881,27 +3905,27 @@
         <v>24</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>31</v>
@@ -3910,16 +3934,16 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>23</v>
@@ -3928,27 +3952,27 @@
         <v>35</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L56" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O56" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O56" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>31</v>
@@ -3957,16 +3981,16 @@
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I57" s="2" t="s">
         <v>23</v>
@@ -3975,45 +3999,45 @@
         <v>35</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M57" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>23</v>
@@ -4022,27 +4046,27 @@
         <v>24</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L58" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>31</v>
@@ -4051,16 +4075,16 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>23</v>
@@ -4069,27 +4093,27 @@
         <v>24</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O59" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>31</v>
@@ -4098,16 +4122,16 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
@@ -4116,27 +4140,27 @@
         <v>24</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="L60" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O60" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>31</v>
@@ -4145,10 +4169,10 @@
         <v>42</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>21</v>
@@ -4163,27 +4187,27 @@
         <v>24</v>
       </c>
       <c r="K61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L61" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M61" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>81</v>
+        <v>226</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
@@ -4192,10 +4216,10 @@
         <v>42</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>44</v>
@@ -4207,30 +4231,30 @@
         <v>46</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="L62" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O62" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>31</v>
@@ -4239,10 +4263,10 @@
         <v>42</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>21</v>
@@ -4257,27 +4281,27 @@
         <v>24</v>
       </c>
       <c r="K63" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L63" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L63" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M63" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O63" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>81</v>
+        <v>230</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
@@ -4286,10 +4310,10 @@
         <v>42</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>44</v>
@@ -4301,30 +4325,30 @@
         <v>46</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O64" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>17</v>
@@ -4333,10 +4357,10 @@
         <v>42</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>44</v>
@@ -4351,27 +4375,27 @@
         <v>24</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O65" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>31</v>
@@ -4380,10 +4404,10 @@
         <v>42</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>21</v>
@@ -4398,27 +4422,27 @@
         <v>24</v>
       </c>
       <c r="K66" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L66" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="L66" s="2" t="s">
-        <v>26</v>
-      </c>
       <c r="M66" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O66" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>81</v>
+        <v>236</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>17</v>
@@ -4427,10 +4451,10 @@
         <v>42</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>44</v>
@@ -4442,22 +4466,22 @@
         <v>46</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O67" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -4465,7 +4489,7 @@
         <v>47</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>31</v>
@@ -4474,10 +4498,10 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>21</v>
@@ -4492,27 +4516,27 @@
         <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O68" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>31</v>
@@ -4521,10 +4545,10 @@
         <v>42</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>44</v>
@@ -4536,30 +4560,30 @@
         <v>46</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O69" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>81</v>
+        <v>241</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
@@ -4568,10 +4592,10 @@
         <v>42</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>44</v>
@@ -4583,22 +4607,22 @@
         <v>46</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O70" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
@@ -4606,7 +4630,7 @@
         <v>47</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>31</v>
@@ -4615,10 +4639,10 @@
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>21</v>
@@ -4630,30 +4654,30 @@
         <v>23</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O71" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>16</v>
+        <v>245</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>31</v>
@@ -4662,57 +4686,57 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>44</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="L72" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O72" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>93</v>
+        <v>249</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>21</v>
@@ -4724,22 +4748,22 @@
         <v>46</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O73" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
@@ -4747,7 +4771,7 @@
         <v>47</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>31</v>
@@ -4756,10 +4780,10 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>21</v>
@@ -4771,42 +4795,42 @@
         <v>23</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O74" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>93</v>
+        <v>253</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>21</v>
@@ -4818,22 +4842,22 @@
         <v>46</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>25</v>
+        <v>108</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
@@ -4841,7 +4865,7 @@
         <v>47</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>31</v>
@@ -4850,10 +4874,10 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>21</v>
@@ -4865,42 +4889,42 @@
         <v>23</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="L76" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>93</v>
+        <v>256</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>21</v>
@@ -4912,30 +4936,30 @@
         <v>46</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>219</v>
+        <v>51</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>31</v>
@@ -4944,10 +4968,10 @@
         <v>42</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>21</v>
@@ -4959,116 +4983,116 @@
         <v>46</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>233</v>
+        <v>100</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O78" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>252</v>
+        <v>51</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="O79" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>113</v>
+        <v>45</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -5084,23 +5108,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="E2" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5108,16 +5132,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5128,15 +5152,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>62</v>
+        <v>28.06</v>
       </c>
       <c r="J5" s="4">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5149,7 +5173,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -5157,7 +5181,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5188,12 +5212,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="B2">
         <v>79</v>
@@ -5207,43 +5231,43 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>62</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -5252,13 +5276,13 @@
         <v>58</v>
       </c>
       <c r="G10" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5270,18 +5294,18 @@
         <v>38</v>
       </c>
       <c r="P10" t="s">
-        <v>279</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>1</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11" t="s">
         <v>17</v>
@@ -5296,33 +5320,33 @@
         <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="K11">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="M11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N11">
         <v>20</v>
       </c>
       <c r="P11" t="s">
-        <v>28</v>
+        <v>264</v>
       </c>
       <c r="Q11">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -5334,118 +5358,138 @@
         <v>54</v>
       </c>
       <c r="J12" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="K12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="N12">
         <v>4</v>
       </c>
       <c r="P12" t="s">
-        <v>253</v>
+        <v>289</v>
       </c>
       <c r="Q12">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>53</v>
       </c>
       <c r="B13">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="E13">
         <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="N13">
         <v>7</v>
       </c>
-      <c r="P13" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>205</v>
+        <v>60</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
-      <c r="P14" t="s">
-        <v>39</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="N15">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
       <c r="M16" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="N16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="13:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
       <c r="M17" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>141</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
       <c r="D19" s="6" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5453,7 +5497,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5461,142 +5505,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>117</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>96</v>
+        <v>142</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>119</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F22" s="2">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="F23" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>71</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="F24" s="2">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>171</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F25" s="2">
-        <v>69</v>
+        <v>142</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F26" s="2">
-        <v>57</v>
+        <v>142</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F27" s="2">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F28" s="2">
-        <v>56</v>
+        <v>142</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="F30" s="2">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
